--- a/healthcare_forms/012_healthcare_uniform_order_form--healthcare_forms.xlsx
+++ b/healthcare_forms/012_healthcare_uniform_order_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Select Size</t>
+          <t>Preferred uniform size</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Select Style</t>
+          <t>Preferred uniform style</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Select Color</t>
+          <t>Preferred uniform color</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Date Required</t>
+          <t>Date required</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Select Time</t>
+          <t>Preferred delivery time</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Additional notes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email for follow-up</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Select one</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Select multiple</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Preferred delivery date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Select One 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Select Multiple 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_size_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Select Size 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>select_style</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Select Style</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1284,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,267 +1208,165 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_size_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_size_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_size_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_style_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>button-down</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Button-Down</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_style_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>polo</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Polo</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_style_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>scrubs</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Scrubs</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
